--- a/diseases/d115/2000-2004.xlsx
+++ b/diseases/d115/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.7110352673492605</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2397,9 +2388,6 @@
       <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -2941,9 +2929,6 @@
       <c r="O14" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -3485,9 +3470,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3881,9 +3863,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -4425,9 +4404,6 @@
       <c r="O22" t="n">
         <v>4</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -4969,9 +4945,6 @@
       <c r="O25" t="n">
         <v>6</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.1159151165193241</v>
       </c>
@@ -5513,9 +5486,6 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -6057,9 +6027,6 @@
       <c r="O31" t="n">
         <v>3</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -6601,9 +6568,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7145,9 +7109,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7689,9 +7650,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8085,9 +8043,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.3508125696143693</v>
       </c>
@@ -8481,9 +8436,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8777,9 +8729,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -9173,9 +9122,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -9469,9 +9415,6 @@
       <c r="O50" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -9865,9 +9808,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10161,9 +10101,6 @@
       <c r="O54" t="n">
         <v>3</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -10557,9 +10494,6 @@
       <c r="O56" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.004251387248916258</v>
       </c>
@@ -10853,9 +10787,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11249,9 +11180,6 @@
       <c r="O60" t="n">
         <v>3</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.006377080873374387</v>
       </c>
@@ -11545,9 +11473,6 @@
       <c r="O62" t="n">
         <v>3</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -11941,9 +11866,6 @@
       <c r="O64" t="n">
         <v>2</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.004251387248916258</v>
       </c>
@@ -12237,9 +12159,6 @@
       <c r="O66" t="n">
         <v>1</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -12633,9 +12552,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -12929,9 +12845,6 @@
       <c r="O70" t="n">
         <v>3</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -13325,9 +13238,6 @@
       <c r="O72" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.004251387248916258</v>
       </c>
@@ -13621,9 +13531,6 @@
       <c r="O74" t="n">
         <v>2</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -14017,9 +13924,6 @@
       <c r="O76" t="n">
         <v>2</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.004251387248916258</v>
       </c>
@@ -14313,9 +14217,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -14709,9 +14610,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -15005,9 +14903,6 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -15401,9 +15296,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -15697,9 +15589,6 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -16093,9 +15982,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -16389,9 +16275,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -16785,9 +16668,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -17181,9 +17061,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -17477,9 +17354,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -17873,9 +17747,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -18169,9 +18040,6 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -18565,9 +18433,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -18861,9 +18726,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -19257,9 +19119,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -19553,9 +19412,6 @@
       <c r="O108" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -19949,9 +19805,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -20245,9 +20098,6 @@
       <c r="O112" t="n">
         <v>4</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.07691500084798789</v>
       </c>
@@ -20641,9 +20491,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -20937,9 +20784,6 @@
       <c r="O116" t="n">
         <v>4</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.07691500084798789</v>
       </c>
@@ -21333,9 +21177,6 @@
       <c r="O118" t="n">
         <v>1</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -21629,9 +21470,6 @@
       <c r="O120" t="n">
         <v>3</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -22025,9 +21863,6 @@
       <c r="O122" t="n">
         <v>1</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -22321,9 +22156,6 @@
       <c r="O124" t="n">
         <v>1</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -22717,9 +22549,6 @@
       <c r="O126" t="n">
         <v>3</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.006342612649636899</v>
       </c>
@@ -23013,9 +22842,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -23409,9 +23235,6 @@
       <c r="O130" t="n">
         <v>1</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -23705,9 +23528,6 @@
       <c r="O132" t="n">
         <v>2</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -24101,9 +23921,6 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -24397,9 +24214,6 @@
       <c r="O136" t="n">
         <v>1</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -24793,9 +24607,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -25089,9 +24900,6 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -25485,9 +25293,6 @@
       <c r="O142" t="n">
         <v>2</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.690595811536403</v>
       </c>
@@ -25881,9 +25686,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -26177,9 +25979,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -26573,9 +26372,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -26869,9 +26665,6 @@
       <c r="O150" t="n">
         <v>2</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -27265,9 +27058,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -27561,9 +27351,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -27957,9 +27744,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -28253,9 +28037,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -28649,9 +28430,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -28945,9 +28723,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -29341,9 +29116,6 @@
       <c r="O164" t="n">
         <v>19</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.03998807892228255</v>
       </c>
@@ -29637,9 +29409,6 @@
       <c r="O166" t="n">
         <v>6</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.1150978667569545</v>
       </c>
@@ -30033,9 +29802,6 @@
       <c r="O168" t="n">
         <v>21</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.04419735038778597</v>
       </c>
@@ -30329,9 +30095,6 @@
       <c r="O170" t="n">
         <v>1</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -30725,9 +30488,6 @@
       <c r="O172" t="n">
         <v>4</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.008418542931006853</v>
       </c>
@@ -31021,9 +30781,6 @@
       <c r="O174" t="n">
         <v>1</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -31417,9 +31174,6 @@
       <c r="O176" t="n">
         <v>1</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -31713,9 +31467,6 @@
       <c r="O178" t="n">
         <v>1</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -32109,9 +31860,6 @@
       <c r="O180" t="n">
         <v>5</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.01052317866375857</v>
       </c>
@@ -32405,9 +32153,6 @@
       <c r="O182" t="n">
         <v>1</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -32801,9 +32546,6 @@
       <c r="O184" t="n">
         <v>1</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -33097,9 +32839,6 @@
       <c r="O186" t="n">
         <v>2</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -33493,9 +33232,6 @@
       <c r="O188" t="n">
         <v>1</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -33789,9 +33525,6 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -34185,9 +33918,6 @@
       <c r="O192" t="n">
         <v>5</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>1.711341229461766</v>
       </c>
@@ -34581,9 +34311,6 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -34877,9 +34604,6 @@
       <c r="O196" t="n">
         <v>2</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -35273,9 +34997,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -35569,9 +35290,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -35965,9 +35683,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -36261,9 +35976,6 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -36657,9 +36369,6 @@
       <c r="O206" t="n">
         <v>1</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -36953,9 +36662,6 @@
       <c r="O208" t="n">
         <v>1</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -37349,9 +37055,6 @@
       <c r="O210" t="n">
         <v>1</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -37645,9 +37348,6 @@
       <c r="O212" t="n">
         <v>2</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -38041,9 +37741,6 @@
       <c r="O214" t="n">
         <v>4</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.008386258398588819</v>
       </c>
@@ -38337,9 +38034,6 @@
       <c r="O216" t="n">
         <v>3</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -38733,9 +38427,6 @@
       <c r="O218" t="n">
         <v>75</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.1572423449735404</v>
       </c>
@@ -39029,9 +38720,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -39425,9 +39113,6 @@
       <c r="O222" t="n">
         <v>30</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.06289693798941615</v>
       </c>
@@ -39721,9 +39406,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -40117,9 +39799,6 @@
       <c r="O226" t="n">
         <v>6</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.01257938759788323</v>
       </c>
@@ -40413,9 +40092,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -40809,9 +40485,6 @@
       <c r="O230" t="n">
         <v>1</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -41105,9 +40778,6 @@
       <c r="O232" t="n">
         <v>1</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -41501,9 +41171,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -41797,9 +41464,6 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -42191,9 +41855,6 @@
         <v>0</v>
       </c>
       <c r="O238" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q238" t="n">
         <v>0</v>
       </c>
       <c r="R238" t="n">
